--- a/jogos_2024-09-18.xlsx
+++ b/jogos_2024-09-18.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,22 +901,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Shimizu S-Pulse</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.35</v>
+        <v>4.1</v>
       </c>
       <c r="M4" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="O4" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="P4" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.45</v>
+        <v>2.38</v>
       </c>
       <c r="R4" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>2.55</v>
+        <v>2.81</v>
       </c>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U4" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="V4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="X4" t="n">
-        <v>2.93</v>
+        <v>3.18</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.16</v>
+        <v>1.85</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.64</v>
+        <v>3.28</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['14', '44', '78']</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['71', '77']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.4</v>
+        <v>1.88</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.5</v>
+        <v>1.19</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.95</v>
+        <v>2.64</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45553.29166666666</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,23 +1030,23 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shimizu S-Pulse</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>2</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.1</v>
+        <v>2.35</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N5" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.38</v>
+        <v>3.45</v>
       </c>
       <c r="R5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>['14', '44', '78']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
         <v>1.4</v>
       </c>
-      <c r="S5" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X5" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>['63']</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>['71', '77']</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AH5" t="n">
-        <v>1.19</v>
+        <v>1.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.64</v>
+        <v>1.95</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45553.29166666666</v>
@@ -1417,20 +1417,20 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Zrinski Jurjevac</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
         <v>2</v>
       </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O8" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="P8" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
         <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="T8" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W8" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="X8" t="n">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AA8" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
           <t>['-1', '-1']</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>['-1']</t>
-        </is>
-      </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AI8" t="n">
         <v>1.67</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45553.47916666666</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zrinski Jurjevac</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>2</v>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="M9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T9" t="n">
         <v>3</v>
       </c>
-      <c r="N9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>4</v>
-      </c>
-      <c r="R9" t="n">
+      <c r="U9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>['-1', '-1']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>['-1', '-1']</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
         <v>1.5</v>
       </c>
-      <c r="S9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>['-1', '-1']</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH9" t="n">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.67</v>
+        <v>2.07</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.63</v>
+        <v>2.03</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45553.47916666666</v>
@@ -1675,19 +1675,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1701,31 +1701,31 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.62</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>2.63</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U10" t="n">
         <v>1.33</v>
@@ -1734,50 +1734,50 @@
         <v>1.05</v>
       </c>
       <c r="W10" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="X10" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="Y10" t="n">
         <v>2.1</v>
       </c>
       <c r="Z10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>['-1', '-1']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>['-1']</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.65</v>
       </c>
-      <c r="AA10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>['-1', '-1']</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>['-1', '-1']</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AI10" t="n">
-        <v>2.07</v>
+        <v>1.67</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45553.47916666666</v>
@@ -1794,119 +1794,119 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.15</v>
+        <v>7.5</v>
       </c>
       <c r="M11" t="n">
-        <v>5.16</v>
+        <v>4.1</v>
       </c>
       <c r="N11" t="n">
-        <v>9.31</v>
+        <v>1.45</v>
       </c>
       <c r="O11" t="n">
-        <v>1.57</v>
+        <v>7</v>
       </c>
       <c r="P11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S11" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q11" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.8</v>
-      </c>
       <c r="T11" t="n">
-        <v>2.14</v>
+        <v>2.82</v>
       </c>
       <c r="U11" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="X11" t="n">
-        <v>5.2</v>
+        <v>3.56</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.37</v>
+        <v>1.95</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.85</v>
+        <v>1.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.93</v>
+        <v>3.18</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.75</v>
+        <v>1.32</v>
       </c>
       <c r="AC11" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['11', '56', '83']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['32']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.02</v>
+        <v>2.65</v>
       </c>
       <c r="AH11" t="n">
-        <v>4.33</v>
+        <v>1.1</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.17</v>
+        <v>4</v>
       </c>
       <c r="AJ11" t="n">
-        <v>5</v>
+        <v>1.33</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45553.47916666666</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,22 +1933,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.29</v>
+        <v>2.13</v>
       </c>
       <c r="M12" t="n">
-        <v>4.6</v>
+        <v>3.12</v>
       </c>
       <c r="N12" t="n">
-        <v>9</v>
+        <v>2.77</v>
       </c>
       <c r="O12" t="n">
+        <v>3</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.73</v>
       </c>
-      <c r="P12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>10</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X12" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC12" t="n">
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>['-1', '-1']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>2.38</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>['38', '90+3']</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>['84']</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>5.5</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45553.47916666666</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,25 +2062,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>7.5</v>
+        <v>1.29</v>
       </c>
       <c r="M13" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="N13" t="n">
+        <v>9</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>10</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X13" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AB13" t="n">
         <v>1.45</v>
       </c>
-      <c r="O13" t="n">
-        <v>7</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X13" t="n">
+      <c r="AC13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>['38', '90+3']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>['84']</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AH13" t="n">
         <v>3.56</v>
       </c>
-      <c r="Y13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>['32']</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AI13" t="n">
-        <v>4</v>
+        <v>1.18</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.33</v>
+        <v>5.5</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45553.47916666666</v>
@@ -2181,32 +2181,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2217,65 +2217,65 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.13</v>
+        <v>1.15</v>
       </c>
       <c r="M14" t="n">
-        <v>3.12</v>
+        <v>5.16</v>
       </c>
       <c r="N14" t="n">
-        <v>2.77</v>
+        <v>9.31</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>1.57</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.75</v>
+        <v>8.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="T14" t="n">
-        <v>3.4</v>
+        <v>2.14</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3</v>
+        <v>1.66</v>
       </c>
       <c r="V14" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="X14" t="n">
-        <v>2.88</v>
+        <v>5.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.25</v>
+        <v>1.37</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.62</v>
+        <v>2.85</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.5</v>
+        <v>1.93</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.17</v>
+        <v>1.75</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['-1', '-1']</t>
+          <t>['11', '56', '83']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.31</v>
+        <v>1.02</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.52</v>
+        <v>4.33</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.8</v>
+        <v>1.17</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.38</v>
+        <v>5</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45553.47916666666</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,22 +2320,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vorskla</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.18</v>
+        <v>2.2</v>
       </c>
       <c r="M15" t="n">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>10.5</v>
+        <v>3</v>
       </c>
       <c r="O15" t="n">
-        <v>1.76</v>
+        <v>2.8</v>
       </c>
       <c r="P15" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="S15" t="n">
-        <v>3.55</v>
+        <v>2.95</v>
       </c>
       <c r="T15" t="n">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="U15" t="n">
-        <v>1.66</v>
+        <v>1.45</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W15" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X15" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AC15" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['33', '35', '90+1']</t>
+          <t>['27', '90']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['81']</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.05</v>
+        <v>1.35</v>
       </c>
       <c r="AH15" t="n">
-        <v>4</v>
+        <v>1.62</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.27</v>
+        <v>1.85</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45553.5</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,22 +2449,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Vorskla</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.2</v>
+        <v>1.18</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>10.5</v>
       </c>
       <c r="O16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="P16" t="n">
         <v>2.8</v>
       </c>
-      <c r="P16" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Q16" t="n">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>2.95</v>
+        <v>3.55</v>
       </c>
       <c r="T16" t="n">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="U16" t="n">
-        <v>1.45</v>
+        <v>1.66</v>
       </c>
       <c r="V16" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="X16" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['27', '90']</t>
+          <t>['33', '35', '90+1']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['57']</t>
+          <t>['81']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.35</v>
+        <v>1.05</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.62</v>
+        <v>4</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.85</v>
+        <v>1.27</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45553.5</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="N17" t="n">
-        <v>2.7</v>
+        <v>1.55</v>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>5.05</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>2.51</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.2</v>
+        <v>2.01</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>3.64</v>
       </c>
       <c r="T17" t="n">
-        <v>2.55</v>
+        <v>2.22</v>
       </c>
       <c r="U17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['7', '23', '48', '60']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.45</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>['13', '18', '53', '59']</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>2.05</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45553.54166666666</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,109 +2965,109 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
         <v>2</v>
       </c>
-      <c r="H20" t="n">
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z20" t="n">
         <v>2</v>
       </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="M20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3</v>
-      </c>
-      <c r="R20" t="n">
+      <c r="AA20" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>['13', '18', '53', '59']</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
         <v>1.45</v>
       </c>
-      <c r="S20" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>['46', '64']</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>['14', '57']</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
+      <c r="AH20" t="n">
         <v>1.5</v>
       </c>
-      <c r="AH20" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AI20" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45553.54166666666</v>
@@ -3084,119 +3084,119 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P21" t="n">
         <v>2</v>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L21" t="n">
-        <v>5</v>
-      </c>
-      <c r="M21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="O21" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.51</v>
-      </c>
       <c r="Q21" t="n">
-        <v>2.01</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="S21" t="n">
-        <v>3.64</v>
+        <v>2.56</v>
       </c>
       <c r="T21" t="n">
-        <v>2.22</v>
+        <v>3.15</v>
       </c>
       <c r="U21" t="n">
-        <v>1.62</v>
+        <v>1.31</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W21" t="n">
-        <v>1.16</v>
+        <v>1.57</v>
       </c>
       <c r="X21" t="n">
-        <v>5.5</v>
+        <v>2.25</v>
       </c>
       <c r="Y21" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>['46', '64']</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>['14', '57']</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>['7', '23', '48', '60']</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.43</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45553.54166666666</v>
@@ -3610,25 +3610,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="M25" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="N25" t="n">
-        <v>4.33</v>
+        <v>5.5</v>
       </c>
       <c r="O25" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="P25" t="n">
-        <v>2.25</v>
+        <v>2.69</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.5</v>
+        <v>5.56</v>
       </c>
       <c r="R25" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="S25" t="n">
-        <v>3.22</v>
+        <v>3.9</v>
       </c>
       <c r="T25" t="n">
-        <v>2.55</v>
+        <v>2.19</v>
       </c>
       <c r="U25" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="V25" t="n">
         <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X25" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="Z25" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['14', '29', '54', '80']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['22']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.07</v>
+        <v>2.65</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.62</v>
+        <v>2.95</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45553.58333333334</v>
@@ -3729,26 +3729,26 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="N26" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="O26" t="n">
         <v>2.8</v>
       </c>
       <c r="P26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>['70']</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>2</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>4</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X26" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>['65', '72']</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>2.38</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45553.58333333334</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,22 +3868,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.65</v>
+        <v>4.5</v>
       </c>
       <c r="M27" t="n">
         <v>3.8</v>
       </c>
       <c r="N27" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="O27" t="n">
-        <v>2.1</v>
+        <v>4.75</v>
       </c>
       <c r="P27" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="Q27" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S27" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="T27" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="U27" t="n">
         <v>1.5</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W27" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="X27" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="Z27" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AC27" t="n">
         <v>1.67</v>
       </c>
       <c r="AD27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
         <v>2.15</v>
       </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>['23']</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>['48', '88']</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AH27" t="n">
-        <v>2.18</v>
+        <v>1.15</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.48</v>
+        <v>2.88</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.7</v>
+        <v>1.44</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45553.58333333334</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,19 +3997,19 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.5</v>
+        <v>2.25</v>
       </c>
       <c r="M28" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="N28" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="O28" t="n">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="P28" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="R28" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="T28" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U28" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W28" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X28" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="AC28" t="n">
         <v>1.67</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['77', '81']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['52']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>2.15</v>
+        <v>1.28</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.15</v>
+        <v>1.5</v>
       </c>
       <c r="AI28" t="n">
-        <v>2.88</v>
+        <v>1.93</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.44</v>
+        <v>1.94</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45553.58333333334</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,109 +4255,109 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N30" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z30" t="n">
         <v>2</v>
       </c>
-      <c r="H30" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="M30" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N30" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T30" t="n">
+      <c r="AA30" t="n">
         <v>2.75</v>
       </c>
-      <c r="U30" t="n">
+      <c r="AB30" t="n">
         <v>1.4</v>
       </c>
-      <c r="V30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X30" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AC30" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['77', '81']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['52']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.5</v>
+        <v>2.07</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.93</v>
+        <v>1.57</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.94</v>
+        <v>2.62</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45553.58333333334</v>
@@ -4374,119 +4374,119 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G31" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q31" t="n">
         <v>4</v>
       </c>
-      <c r="H31" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" t="n">
-        <v>2</v>
-      </c>
-      <c r="J31" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N31" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>5.56</v>
-      </c>
       <c r="R31" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="S31" t="n">
-        <v>3.9</v>
+        <v>2.55</v>
       </c>
       <c r="T31" t="n">
-        <v>2.19</v>
+        <v>2.95</v>
       </c>
       <c r="U31" t="n">
-        <v>1.63</v>
+        <v>1.35</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W31" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="X31" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.64</v>
+        <v>1.2</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['14', '29', '54', '80']</t>
+          <t>['65', '72']</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>['22']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.65</v>
+        <v>1.65</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.95</v>
+        <v>2.38</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45553.58333333334</v>
@@ -4513,22 +4513,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G32" t="n">
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -4539,31 +4539,31 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="M32" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="N32" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="O32" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="P32" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="R32" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S32" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="T32" t="n">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="U32" t="n">
         <v>1.5</v>
@@ -4578,44 +4578,44 @@
         <v>4.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>['70']</t>
+          <t>['23']</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['48', '88']</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.42</v>
+        <v>1.16</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.57</v>
+        <v>2.18</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.82</v>
+        <v>1.48</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45553.58333333334</v>
@@ -4900,48 +4900,48 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M35" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N35" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O35" t="n">
         <v>2</v>
       </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M35" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N35" t="n">
-        <v>6</v>
-      </c>
-      <c r="O35" t="n">
-        <v>2.3</v>
-      </c>
       <c r="P35" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="R35" t="n">
         <v>1.44</v>
@@ -4959,50 +4959,50 @@
         <v>1.03</v>
       </c>
       <c r="W35" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X35" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+4', '90+1']</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>['70', '90+5']</t>
+          <t>['22']</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AJ35" t="n">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45553.60416666666</v>
@@ -5158,25 +5158,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
         <v>2</v>
       </c>
-      <c r="H37" t="n">
-        <v>1</v>
-      </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5184,22 +5184,22 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="M37" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="N37" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="O37" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="P37" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q37" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="R37" t="n">
         <v>1.44</v>
@@ -5217,50 +5217,50 @@
         <v>1.03</v>
       </c>
       <c r="W37" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X37" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="Z37" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>['45+4', '90+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>['22']</t>
+          <t>['70', '90+5']</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AJ37" t="n">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45553.60416666666</v>
@@ -5545,22 +5545,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -5571,83 +5571,83 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.4</v>
+        <v>1.33</v>
       </c>
       <c r="M40" t="n">
-        <v>3.75</v>
+        <v>5.25</v>
       </c>
       <c r="N40" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="O40" t="n">
-        <v>3.75</v>
+        <v>1.83</v>
       </c>
       <c r="P40" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.63</v>
+        <v>7</v>
       </c>
       <c r="R40" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S40" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="T40" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="U40" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="V40" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W40" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X40" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>['17', '47', '56', '70', '86']</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>['60']</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AI40" t="n">
         <v>1.25</v>
       </c>
-      <c r="X40" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>['76', '86', '90+5']</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AJ40" t="n">
-        <v>1.62</v>
+        <v>4</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45553.66666666666</v>
@@ -5674,19 +5674,19 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -5700,62 +5700,62 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="M41" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="N41" t="n">
-        <v>5.75</v>
+        <v>2</v>
       </c>
       <c r="O41" t="n">
-        <v>2.05</v>
+        <v>3.75</v>
       </c>
       <c r="P41" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>5.5</v>
+        <v>2.63</v>
       </c>
       <c r="R41" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S41" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="T41" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="U41" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="V41" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W41" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X41" t="n">
-        <v>4.85</v>
+        <v>4.15</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="Z41" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD41" t="n">
         <v>2.2</v>
       </c>
-      <c r="AA41" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AE41" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5763,20 +5763,20 @@
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['76', '86', '90+5']</t>
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.14</v>
+        <v>1.83</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.59</v>
+        <v>1.32</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.36</v>
+        <v>2.38</v>
       </c>
       <c r="AJ41" t="n">
-        <v>3.1</v>
+        <v>1.62</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45553.66666666666</v>
@@ -5932,22 +5932,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5958,22 +5958,22 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="M43" t="n">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="N43" t="n">
-        <v>8.5</v>
+        <v>5.75</v>
       </c>
       <c r="O43" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="P43" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q43" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="R43" t="n">
         <v>1.29</v>
@@ -5982,10 +5982,10 @@
         <v>3.5</v>
       </c>
       <c r="T43" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="U43" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="V43" t="n">
         <v>1.03</v>
@@ -6003,38 +6003,38 @@
         <v>2.2</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>['17', '47', '56', '70', '86']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>['60']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AH43" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AJ43" t="n">
         <v>3.1</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>4</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45553.66666666666</v>
@@ -6577,25 +6577,25 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -6603,22 +6603,22 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.73</v>
+        <v>3.4</v>
       </c>
       <c r="M48" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="N48" t="n">
-        <v>4</v>
+        <v>1.95</v>
       </c>
       <c r="O48" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="P48" t="n">
         <v>2.4</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.33</v>
+        <v>2.63</v>
       </c>
       <c r="R48" t="n">
         <v>1.29</v>
@@ -6633,19 +6633,19 @@
         <v>1.57</v>
       </c>
       <c r="V48" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W48" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X48" t="n">
-        <v>4.92</v>
+        <v>5.5</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AA48" t="n">
         <v>2.25</v>
@@ -6654,32 +6654,32 @@
         <v>1.57</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>['45+5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>['15', '25', '31', '74', '85']</t>
+          <t>['51', '70']</t>
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.25</v>
+        <v>1.78</v>
       </c>
       <c r="AH48" t="n">
-        <v>2.1</v>
+        <v>1.42</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="AJ48" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45553.85416666666</v>
@@ -6706,16 +6706,16 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H49" t="n">
         <v>2</v>
@@ -6724,7 +6724,7 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -6732,43 +6732,43 @@
         </is>
       </c>
       <c r="L49" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="M49" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N49" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O49" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P49" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S49" t="n">
         <v>3.4</v>
       </c>
-      <c r="M49" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N49" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="O49" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P49" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S49" t="n">
-        <v>3.5</v>
-      </c>
       <c r="T49" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="U49" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="V49" t="n">
         <v>1.01</v>
       </c>
       <c r="W49" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X49" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="Y49" t="n">
         <v>1.53</v>
@@ -6777,38 +6777,38 @@
         <v>2.35</v>
       </c>
       <c r="AA49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD49" t="n">
         <v>2.25</v>
       </c>
-      <c r="AB49" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['56', '84']</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>['51', '70']</t>
+          <t>['29', '59']</t>
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.78</v>
+        <v>1.52</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="AI49" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AJ49" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45553.85416666666</v>
@@ -6835,25 +6835,25 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -6861,55 +6861,55 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.63</v>
+        <v>1.73</v>
       </c>
       <c r="M50" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="N50" t="n">
-        <v>2.38</v>
+        <v>4</v>
       </c>
       <c r="O50" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="P50" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S50" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X50" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z50" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q50" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S50" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T50" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X50" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AA50" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AC50" t="n">
         <v>1.57</v>
@@ -6919,25 +6919,25 @@
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>['56', '84']</t>
+          <t>['45+5']</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>['29', '59']</t>
+          <t>['15', '25', '31', '74', '85']</t>
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.51</v>
+        <v>2.1</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="AJ50" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45553.85416666666</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,19 +7351,19 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
         <v>1</v>
@@ -7377,83 +7377,83 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="M54" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N54" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="O54" t="n">
         <v>2.5</v>
       </c>
       <c r="P54" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R54" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="S54" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="T54" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="U54" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X54" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>['6', '52']</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG54" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI54" t="n">
         <v>1.5</v>
       </c>
-      <c r="V54" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X54" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>['45+7']</t>
-        </is>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>['73']</t>
-        </is>
-      </c>
-      <c r="AG54" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AJ54" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AK54" s="3" t="n">
         <v>45553.89583333334</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,22 +7480,22 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -7506,80 +7506,80 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="M55" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N55" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="O55" t="n">
         <v>2.5</v>
       </c>
       <c r="P55" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q55" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="R55" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="S55" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="T55" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U55" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V55" t="n">
         <v>1.06</v>
       </c>
       <c r="W55" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="X55" t="n">
-        <v>3.1</v>
+        <v>2.71</v>
       </c>
       <c r="Y55" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AA55" t="n">
-        <v>4.1</v>
+        <v>4.73</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AC55" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG55" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH55" t="n">
         <v>2</v>
       </c>
-      <c r="AD55" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>['6', '52']</t>
-        </is>
-      </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG55" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AI55" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AJ55" t="n">
         <v>3</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,25 +7609,25 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -7635,83 +7635,83 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="M56" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N56" t="n">
-        <v>4.33</v>
+        <v>2.7</v>
       </c>
       <c r="O56" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="P56" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="Q56" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S56" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X56" t="n">
         <v>5.5</v>
       </c>
-      <c r="R56" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S56" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T56" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U56" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V56" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W56" t="n">
+      <c r="Y56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>['54']</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>['33', '45+1']</t>
+        </is>
+      </c>
+      <c r="AG56" t="n">
         <v>1.47</v>
       </c>
-      <c r="X56" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG56" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AH56" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AI56" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AJ56" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="AK56" s="3" t="n">
         <v>45553.89583333334</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,25 +7738,25 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G57" t="n">
+        <v>3</v>
+      </c>
+      <c r="H57" t="n">
         <v>1</v>
       </c>
-      <c r="H57" t="n">
-        <v>2</v>
-      </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -7764,83 +7764,83 @@
         </is>
       </c>
       <c r="L57" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N57" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O57" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P57" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>4</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S57" t="n">
         <v>2.38</v>
       </c>
-      <c r="M57" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N57" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O57" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P57" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R57" t="n">
+      <c r="T57" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U57" t="n">
         <v>1.25</v>
       </c>
-      <c r="S57" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T57" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U57" t="n">
-        <v>1.57</v>
-      </c>
       <c r="V57" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W57" t="n">
-        <v>1.11</v>
+        <v>1.49</v>
       </c>
       <c r="X57" t="n">
-        <v>5.5</v>
+        <v>2.44</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.5</v>
+        <v>2.15</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.1</v>
+        <v>4.75</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.65</v>
+        <v>1.18</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AD57" t="n">
-        <v>2.63</v>
+        <v>1.83</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>['54']</t>
+          <t>['61', '64', '83']</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>['33', '45+1']</t>
+          <t>['79']</t>
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AI57" t="n">
         <v>1.73</v>
       </c>
       <c r="AJ57" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AK57" s="3" t="n">
         <v>45553.89583333334</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,23 +7867,23 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
         <v>1</v>
       </c>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
@@ -7893,83 +7893,83 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="M58" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="N58" t="n">
         <v>3.4</v>
       </c>
       <c r="O58" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="P58" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q58" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S58" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W58" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X58" t="n">
         <v>4</v>
       </c>
-      <c r="R58" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S58" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T58" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U58" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V58" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W58" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="X58" t="n">
-        <v>2.44</v>
-      </c>
       <c r="Y58" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="AA58" t="n">
-        <v>4.75</v>
+        <v>2.9</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="AC58" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>['61', '64', '83']</t>
+          <t>['19']</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>['79']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="AI58" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AJ58" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AK58" s="3" t="n">
         <v>45553.89583333334</v>
@@ -7996,16 +7996,16 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H59" t="n">
         <v>1</v>
@@ -8022,83 +8022,83 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="M59" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N59" t="n">
-        <v>2.9</v>
+        <v>4.33</v>
       </c>
       <c r="O59" t="n">
         <v>2.5</v>
       </c>
       <c r="P59" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>4</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S59" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T59" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q59" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R59" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S59" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T59" t="n">
-        <v>2.1</v>
-      </c>
       <c r="U59" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="V59" t="n">
         <v>1.01</v>
       </c>
       <c r="W59" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X59" t="n">
-        <v>5.35</v>
+        <v>4.8</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AD59" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>['8', '49', '69', '82']</t>
+          <t>['45+7']</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>['75']</t>
+          <t>['73']</t>
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AI59" t="n">
         <v>1.57</v>
       </c>
       <c r="AJ59" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AK59" s="3" t="n">
         <v>45553.89583333334</v>
@@ -8125,19 +8125,19 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G60" t="n">
+        <v>4</v>
+      </c>
+      <c r="H60" t="n">
         <v>1</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
       </c>
       <c r="I60" t="n">
         <v>1</v>
@@ -8151,80 +8151,80 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="M60" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N60" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O60" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P60" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q60" t="n">
         <v>3.6</v>
       </c>
-      <c r="N60" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O60" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P60" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q60" t="n">
+      <c r="R60" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S60" t="n">
         <v>3.75</v>
       </c>
-      <c r="R60" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S60" t="n">
-        <v>3.25</v>
-      </c>
       <c r="T60" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W60" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X60" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD60" t="n">
         <v>2.63</v>
       </c>
-      <c r="U60" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V60" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W60" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X60" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>['19']</t>
+          <t>['8', '49', '69', '82']</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['75']</t>
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AI60" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AJ60" t="n">
         <v>2.3</v>
@@ -8512,16 +8512,16 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H63" t="n">
         <v>2</v>
@@ -8538,83 +8538,83 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.3</v>
+        <v>2.05</v>
       </c>
       <c r="M63" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="N63" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O63" t="n">
-        <v>1.91</v>
+        <v>2.63</v>
       </c>
       <c r="P63" t="n">
         <v>2.6</v>
       </c>
       <c r="Q63" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="R63" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="S63" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="T63" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="U63" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="V63" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W63" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="X63" t="n">
-        <v>4.55</v>
+        <v>6.35</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="Z63" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.63</v>
+        <v>2</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.95</v>
+        <v>3.25</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>['21', '39']</t>
+          <t>['17', '39', '51', '80']</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>['15', '89']</t>
+          <t>['45+3', '58']</t>
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>1.09</v>
+        <v>1.42</v>
       </c>
       <c r="AH63" t="n">
-        <v>2.95</v>
+        <v>1.68</v>
       </c>
       <c r="AI63" t="n">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AJ63" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="AK63" s="3" t="n">
         <v>45553.97916666666</v>
@@ -8641,22 +8641,22 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
         <v>1</v>
@@ -8667,83 +8667,83 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.05</v>
+        <v>1.35</v>
       </c>
       <c r="M64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N64" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="O64" t="n">
-        <v>2.63</v>
+        <v>1.95</v>
       </c>
       <c r="P64" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="R64" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="S64" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="T64" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="U64" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="V64" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W64" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X64" t="n">
-        <v>6.35</v>
+        <v>4.75</v>
       </c>
       <c r="Y64" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>['62']</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>['45+2']</t>
+        </is>
+      </c>
+      <c r="AG64" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AI64" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z64" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD64" t="n">
+      <c r="AJ64" t="n">
         <v>3.25</v>
-      </c>
-      <c r="AE64" t="inlineStr">
-        <is>
-          <t>['17', '39', '51', '80']</t>
-        </is>
-      </c>
-      <c r="AF64" t="inlineStr">
-        <is>
-          <t>['45+3', '58']</t>
-        </is>
-      </c>
-      <c r="AG64" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AH64" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AI64" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ64" t="n">
-        <v>2.1</v>
       </c>
       <c r="AK64" s="3" t="n">
         <v>45553.97916666666</v>
@@ -8770,22 +8770,22 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J65" t="n">
         <v>1</v>
@@ -8796,19 +8796,19 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="M65" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="N65" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="O65" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="P65" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q65" t="n">
         <v>6</v>
@@ -8829,16 +8829,16 @@
         <v>1.02</v>
       </c>
       <c r="W65" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X65" t="n">
-        <v>4.75</v>
+        <v>4.55</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Z65" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AA65" t="n">
         <v>2.15</v>
@@ -8847,32 +8847,32 @@
         <v>1.63</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AD65" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>['62']</t>
+          <t>['21', '39']</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>['45+2']</t>
+          <t>['15', '89']</t>
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AH65" t="n">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="AI65" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AJ65" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AK65" s="3" t="n">
         <v>45553.97916666666</v>
